--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE920BC-AD63-B743-B691-B81A9C4485AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B174B74A-981A-7D4B-AE4A-230B06B81B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="1780" windowWidth="15260" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="1780" windowWidth="20960" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -1170,6 +1170,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1190,6 +1191,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2]</t>
@@ -1215,6 +1217,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1235,6 +1238,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1255,6 +1259,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1]</t>
@@ -1280,6 +1285,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1300,6 +1306,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1320,6 +1327,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -1574,6 +1582,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -1594,6 +1603,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -1623,6 +1633,27 @@
       <t>]</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconResourceKey</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_shopping_square_shop3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_shopping_square_shop2</t>
+  </si>
+  <si>
+    <t>CottonCandy</t>
+  </si>
+  <si>
+    <t>img_shopping_square_shop1</t>
   </si>
 </sst>
 </file>
@@ -2002,7 +2033,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="2" customWidth="1"/>
@@ -2011,7 +2042,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2027,8 +2058,11 @@
       <c r="E1" s="9" t="s">
         <v>30</v>
       </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2044,8 +2078,11 @@
       <c r="E2" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="F2" s="8" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="15">
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2058,11 +2095,14 @@
       <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>31</v>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -2075,8 +2115,14 @@
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="E4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
@@ -2089,10 +2135,13 @@
       <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" ht="13"/>
-    <row r="7" spans="1:5" ht="13"/>
-    <row r="12" spans="1:5" ht="13">
+    <row r="6" spans="1:6" ht="13"/>
+    <row r="7" spans="1:6" ht="13"/>
+    <row r="12" spans="1:6" ht="13">
       <c r="E12" s="1"/>
     </row>
   </sheetData>
